--- a/docs/asset-management/master-asset-tracker.xlsx
+++ b/docs/asset-management/master-asset-tracker.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbe3ec4ce08ab40ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Assets" sheetId="2" r:id="Re9a0bcf546514554"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Audio" sheetId="3" r:id="R7e059d6d6060494d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio Assets" sheetId="4" r:id="R846989ff0898467e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio Changes" sheetId="5" r:id="R567be5bfc76f4e77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="6" r:id="R7715f4fa0d7c4ae5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R0b6cb0d653f34c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Assets" sheetId="2" r:id="Reb10c13f6c084f6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Runtime Audio" sheetId="3" r:id="R4d5283190cac4f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio Assets" sheetId="4" r:id="R6c0098ddf3e140a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio Changes" sheetId="5" r:id="R1df8a6cacd814ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="6" r:id="R7367737d97e241c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -119,7 +119,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="77">
+  <x:cellXfs count="78">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -285,6 +285,7 @@
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -655,7 +656,7 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="30" t="str">
-        <x:v>Current baseline: PromptCraft v137 | Organized visual assets, runtime audio, and recording plan</x:v>
+        <x:v>Current baseline: PROMPTCRAFT_V429 | asset manifest v144 | documentation/cache revision 446</x:v>
       </x:c>
       <x:c r="B2" s="30"/>
       <x:c r="C2" s="30"/>
@@ -673,48 +674,42 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="37" t="str">
-        <x:v>Visual rows</x:v>
+        <x:v>Runtime images</x:v>
       </x:c>
       <x:c r="B4" s="37" t="str">
-        <x:v>Existing image files</x:v>
+        <x:v>Planned runtime images</x:v>
       </x:c>
       <x:c r="C4" s="37" t="str">
-        <x:v>Planned portraits</x:v>
+        <x:v>Reference images</x:v>
       </x:c>
       <x:c r="D4" s="37" t="str">
-        <x:v>Runtime audio files</x:v>
+        <x:v>Runtime audio</x:v>
       </x:c>
       <x:c r="E4" s="37" t="str">
-        <x:v>Dialogue lines</x:v>
+        <x:v>Planned audio</x:v>
       </x:c>
       <x:c r="F4" s="37" t="str">
-        <x:v>S2 draft recordings</x:v>
+        <x:v>Active structured dialogue</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="45" t="n">
-        <x:f>COUNTA('Visual Assets'!C2:C200)</x:f>
-        <x:v>64</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B5" s="45" t="n">
-        <x:f>COUNTIF('Visual Assets'!J2:J200,"In Use")+COUNTIF('Visual Assets'!J2:J200,"Reference Only")</x:f>
-        <x:v>22</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="45" t="n">
-        <x:f>COUNTIF('Visual Assets'!B2:B200,"Student portrait")</x:f>
-        <x:v>36</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D5" s="45" t="n">
-        <x:f>COUNTA('Runtime Audio'!B2:B100)</x:f>
-        <x:v>19</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E5" s="45" t="n">
-        <x:f>COUNTA('Audio Assets'!A2:A250)</x:f>
-        <x:v>115</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F5" s="45" t="n">
-        <x:f>COUNTIF('Audio Assets'!N2:N250,"Planned S2")</x:f>
-        <x:v>12</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -742,7 +737,7 @@
         <x:v>In Use</x:v>
       </x:c>
       <x:c r="B8" s="53" t="str">
-        <x:v>File exists and is referenced by the current v137 runtime.</x:v>
+        <x:v>File is classified by the current V429 runtime/asset manifest.</x:v>
       </x:c>
       <x:c r="C8" s="62"/>
       <x:c r="D8" s="62"/>
@@ -751,10 +746,10 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="52" t="str">
-        <x:v>Reference Only</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="B9" s="53" t="str">
-        <x:v>Concept or drawing reference. It is not loaded by the application.</x:v>
+        <x:v>File/path is prepared but the current scenario/runtime does not load it yet.</x:v>
       </x:c>
       <x:c r="C9" s="62"/>
       <x:c r="D9" s="62"/>
@@ -763,10 +758,10 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="52" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Reference Only</x:v>
       </x:c>
       <x:c r="B10" s="53" t="str">
-        <x:v>Planned production asset with an approved folder path.</x:v>
+        <x:v>Concept/reference material; never loaded as a production runtime asset.</x:v>
       </x:c>
       <x:c r="C10" s="62"/>
       <x:c r="D10" s="62"/>
@@ -775,10 +770,10 @@
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="52" t="str">
-        <x:v>Draft</x:v>
+        <x:v>Not Started</x:v>
       </x:c>
       <x:c r="B11" s="53" t="str">
-        <x:v>Dialogue or asset definition is still being revised. Do not record or finalize yet.</x:v>
+        <x:v>Planned production item with no current file.</x:v>
       </x:c>
       <x:c r="C11" s="62"/>
       <x:c r="D11" s="62"/>
@@ -790,7 +785,7 @@
         <x:v>Archived</x:v>
       </x:c>
       <x:c r="B12" s="53" t="str">
-        <x:v>Preserved from the old implementation but not loaded by the clean-shell runtime.</x:v>
+        <x:v>Historical material preserved for reference but not part of the current runtime.</x:v>
       </x:c>
       <x:c r="C12" s="62"/>
       <x:c r="D12" s="62"/>
@@ -807,7 +802,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="58" t="str">
-        <x:v>S2 note: New Pixel and Jordan recording paths are included as drafts. Record only after the opening dialogue and feedback combinations are locked.</x:v>
+        <x:v>Use assets/asset-manifest.json and current src/ code as source of truth. Trackers document the runtime; they do not override it.</x:v>
       </x:c>
       <x:c r="B14" s="58"/>
       <x:c r="C14" s="58"/>
@@ -925,10 +920,10 @@
       </x:c>
       <x:c r="L2" s="14"/>
       <x:c r="M2" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N2" s="14" t="str">
-        <x:v>Current v137 runtime path. Referenced by style.css.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
@@ -967,10 +962,10 @@
       </x:c>
       <x:c r="L3" s="14"/>
       <x:c r="M3" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N3" s="14" t="str">
-        <x:v>Current v137 runtime path. Referenced by app.js.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
@@ -1009,10 +1004,10 @@
       </x:c>
       <x:c r="L4" s="14"/>
       <x:c r="M4" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N4" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -1051,10 +1046,10 @@
       </x:c>
       <x:c r="L5" s="14"/>
       <x:c r="M5" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N5" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -1093,10 +1088,10 @@
       </x:c>
       <x:c r="L6" s="14"/>
       <x:c r="M6" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N6" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -1135,10 +1130,10 @@
       </x:c>
       <x:c r="L7" s="14"/>
       <x:c r="M7" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N7" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
@@ -1177,10 +1172,10 @@
       </x:c>
       <x:c r="L8" s="14"/>
       <x:c r="M8" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N8" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
@@ -1219,10 +1214,10 @@
       </x:c>
       <x:c r="L9" s="14"/>
       <x:c r="M9" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N9" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
@@ -1261,10 +1256,10 @@
       </x:c>
       <x:c r="L10" s="14"/>
       <x:c r="M10" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N10" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="34" customHeight="1">
@@ -1303,10 +1298,10 @@
       </x:c>
       <x:c r="L11" s="14"/>
       <x:c r="M11" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N11" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="34" customHeight="1">
@@ -1345,10 +1340,10 @@
       </x:c>
       <x:c r="L12" s="14"/>
       <x:c r="M12" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N12" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="34" customHeight="1">
@@ -1387,10 +1382,10 @@
       </x:c>
       <x:c r="L13" s="14"/>
       <x:c r="M13" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N13" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="34" customHeight="1">
@@ -1429,10 +1424,10 @@
       </x:c>
       <x:c r="L14" s="14"/>
       <x:c r="M14" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N14" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="34" customHeight="1">
@@ -1471,10 +1466,10 @@
       </x:c>
       <x:c r="L15" s="14"/>
       <x:c r="M15" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N15" s="14" t="str">
-        <x:v>Current v137 scene path.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
@@ -1506,17 +1501,17 @@
         <x:v>Landscape PNG, 16:9 recommended, 1600×900 or larger</x:v>
       </x:c>
       <x:c r="J16" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="K16" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L16" s="14"/>
       <x:c r="M16" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N16" s="14" t="str">
-        <x:v>Folder currently contains a README placeholder.</x:v>
+        <x:v>Artwork file is present; current app keeps this scenario locked until gameplay is rebuilt.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
@@ -1548,17 +1543,17 @@
         <x:v>Landscape PNG, 16:9 recommended, 1600×900 or larger</x:v>
       </x:c>
       <x:c r="J17" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Planned</x:v>
       </x:c>
       <x:c r="K17" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L17" s="14"/>
       <x:c r="M17" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N17" s="14" t="str">
-        <x:v>Folder currently contains a README placeholder.</x:v>
+        <x:v>Artwork file is present; current app keeps this scenario locked until gameplay is rebuilt.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="34" customHeight="1">
@@ -1597,10 +1592,10 @@
       </x:c>
       <x:c r="L18" s="14"/>
       <x:c r="M18" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N18" s="14" t="str">
-        <x:v>Current v137 runtime asset.</x:v>
+        <x:v>Current V429 runtime asset; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
@@ -1639,10 +1634,10 @@
       </x:c>
       <x:c r="L19" s="14"/>
       <x:c r="M19" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N19" s="14" t="str">
-        <x:v>Use as drawing reference. Not a production portrait.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="34" customHeight="1">
@@ -1681,10 +1676,10 @@
       </x:c>
       <x:c r="L20" s="14"/>
       <x:c r="M20" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N20" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="34" customHeight="1">
@@ -1716,17 +1711,17 @@
         <x:v>Transparent PNG, portrait orientation, match Professor Pixel scale</x:v>
       </x:c>
       <x:c r="J21" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K21" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L21" s="14"/>
       <x:c r="M21" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N21" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="34" customHeight="1">
@@ -1758,17 +1753,17 @@
         <x:v>Transparent PNG, portrait orientation, match Professor Pixel scale</x:v>
       </x:c>
       <x:c r="J22" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K22" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L22" s="14"/>
       <x:c r="M22" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N22" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="34" customHeight="1">
@@ -1800,17 +1795,17 @@
         <x:v>Transparent PNG, portrait orientation, match Professor Pixel scale</x:v>
       </x:c>
       <x:c r="J23" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K23" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L23" s="14"/>
       <x:c r="M23" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N23" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="34" customHeight="1">
@@ -1842,17 +1837,17 @@
         <x:v>Transparent PNG, portrait orientation, match Professor Pixel scale</x:v>
       </x:c>
       <x:c r="J24" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K24" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L24" s="14"/>
       <x:c r="M24" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N24" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="34" customHeight="1">
@@ -1884,17 +1879,17 @@
         <x:v>Transparent PNG, portrait orientation, match Professor Pixel scale</x:v>
       </x:c>
       <x:c r="J25" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>Not Required</x:v>
       </x:c>
       <x:c r="K25" s="14" t="str">
-        <x:v>High</x:v>
+        <x:v>Low</x:v>
       </x:c>
       <x:c r="L25" s="14"/>
       <x:c r="M25" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N25" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Historical planned expression; not present in the current S2 asset registry.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
@@ -1926,17 +1921,17 @@
         <x:v>Transparent PNG, portrait orientation, match Professor Pixel scale</x:v>
       </x:c>
       <x:c r="J26" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K26" s="14" t="str">
         <x:v>High</x:v>
       </x:c>
       <x:c r="L26" s="14"/>
       <x:c r="M26" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N26" s="14" t="str">
-        <x:v>He/him. Feminine-leaning, fashionable, composed, and slightly guarded.</x:v>
+        <x:v>Current S2 production portrait loaded by V429.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="34" customHeight="1">
@@ -1975,10 +1970,10 @@
       </x:c>
       <x:c r="L27" s="14"/>
       <x:c r="M27" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N27" s="14" t="str">
-        <x:v>He/him. Older veteran returning to school in a CTE program. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="34" customHeight="1">
@@ -2017,7 +2012,7 @@
       </x:c>
       <x:c r="L28" s="14"/>
       <x:c r="M28" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N28" s="14" t="str">
         <x:v>He/him. Older veteran returning to school in a CTE program.</x:v>
@@ -2059,7 +2054,7 @@
       </x:c>
       <x:c r="L29" s="14"/>
       <x:c r="M29" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N29" s="14" t="str">
         <x:v>He/him. Older veteran returning to school in a CTE program.</x:v>
@@ -2101,7 +2096,7 @@
       </x:c>
       <x:c r="L30" s="14"/>
       <x:c r="M30" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N30" s="14" t="str">
         <x:v>He/him. Older veteran returning to school in a CTE program.</x:v>
@@ -2143,7 +2138,7 @@
       </x:c>
       <x:c r="L31" s="14"/>
       <x:c r="M31" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N31" s="14" t="str">
         <x:v>He/him. Older veteran returning to school in a CTE program.</x:v>
@@ -2185,7 +2180,7 @@
       </x:c>
       <x:c r="L32" s="14"/>
       <x:c r="M32" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N32" s="14" t="str">
         <x:v>He/him. Older veteran returning to school in a CTE program.</x:v>
@@ -2227,7 +2222,7 @@
       </x:c>
       <x:c r="L33" s="14"/>
       <x:c r="M33" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N33" s="14" t="str">
         <x:v>He/him. Older veteran returning to school in a CTE program.</x:v>
@@ -2269,10 +2264,10 @@
       </x:c>
       <x:c r="L34" s="14"/>
       <x:c r="M34" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N34" s="14" t="str">
-        <x:v>She/her. Rural adult learner balancing several responsibilities. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="34" customHeight="1">
@@ -2311,7 +2306,7 @@
       </x:c>
       <x:c r="L35" s="14"/>
       <x:c r="M35" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N35" s="14" t="str">
         <x:v>She/her. Rural adult learner balancing several responsibilities.</x:v>
@@ -2353,7 +2348,7 @@
       </x:c>
       <x:c r="L36" s="14"/>
       <x:c r="M36" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N36" s="14" t="str">
         <x:v>She/her. Rural adult learner balancing several responsibilities.</x:v>
@@ -2395,7 +2390,7 @@
       </x:c>
       <x:c r="L37" s="14"/>
       <x:c r="M37" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N37" s="14" t="str">
         <x:v>She/her. Rural adult learner balancing several responsibilities.</x:v>
@@ -2437,7 +2432,7 @@
       </x:c>
       <x:c r="L38" s="14"/>
       <x:c r="M38" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N38" s="14" t="str">
         <x:v>She/her. Rural adult learner balancing several responsibilities.</x:v>
@@ -2479,7 +2474,7 @@
       </x:c>
       <x:c r="L39" s="14"/>
       <x:c r="M39" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N39" s="14" t="str">
         <x:v>She/her. Rural adult learner balancing several responsibilities.</x:v>
@@ -2521,7 +2516,7 @@
       </x:c>
       <x:c r="L40" s="14"/>
       <x:c r="M40" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N40" s="14" t="str">
         <x:v>She/her. Rural adult learner balancing several responsibilities.</x:v>
@@ -2563,10 +2558,10 @@
       </x:c>
       <x:c r="L41" s="14"/>
       <x:c r="M41" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N41" s="14" t="str">
-        <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
@@ -2605,7 +2600,7 @@
       </x:c>
       <x:c r="L42" s="14"/>
       <x:c r="M42" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N42" s="14" t="str">
         <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful.</x:v>
@@ -2647,7 +2642,7 @@
       </x:c>
       <x:c r="L43" s="14"/>
       <x:c r="M43" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N43" s="14" t="str">
         <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful.</x:v>
@@ -2689,7 +2684,7 @@
       </x:c>
       <x:c r="L44" s="14"/>
       <x:c r="M44" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N44" s="14" t="str">
         <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful.</x:v>
@@ -2731,7 +2726,7 @@
       </x:c>
       <x:c r="L45" s="14"/>
       <x:c r="M45" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N45" s="14" t="str">
         <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful.</x:v>
@@ -2773,7 +2768,7 @@
       </x:c>
       <x:c r="L46" s="14"/>
       <x:c r="M46" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N46" s="14" t="str">
         <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful.</x:v>
@@ -2815,7 +2810,7 @@
       </x:c>
       <x:c r="L47" s="14"/>
       <x:c r="M47" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N47" s="14" t="str">
         <x:v>She/her. First-generation Native American learner from or near Browning; low-income and resourceful.</x:v>
@@ -2857,10 +2852,10 @@
       </x:c>
       <x:c r="L48" s="14"/>
       <x:c r="M48" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N48" s="14" t="str">
-        <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="34" customHeight="1">
@@ -2899,7 +2894,7 @@
       </x:c>
       <x:c r="L49" s="14"/>
       <x:c r="M49" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N49" s="14" t="str">
         <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic.</x:v>
@@ -2941,7 +2936,7 @@
       </x:c>
       <x:c r="L50" s="14"/>
       <x:c r="M50" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N50" s="14" t="str">
         <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic.</x:v>
@@ -2983,7 +2978,7 @@
       </x:c>
       <x:c r="L51" s="14"/>
       <x:c r="M51" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N51" s="14" t="str">
         <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic.</x:v>
@@ -3025,7 +3020,7 @@
       </x:c>
       <x:c r="L52" s="14"/>
       <x:c r="M52" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N52" s="14" t="str">
         <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic.</x:v>
@@ -3067,7 +3062,7 @@
       </x:c>
       <x:c r="L53" s="14"/>
       <x:c r="M53" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N53" s="14" t="str">
         <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic.</x:v>
@@ -3109,7 +3104,7 @@
       </x:c>
       <x:c r="L54" s="14"/>
       <x:c r="M54" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N54" s="14" t="str">
         <x:v>He/him. Social-media fluent but challenged by institutional technology; may be dyslexic and/or autistic.</x:v>
@@ -3151,10 +3146,10 @@
       </x:c>
       <x:c r="L55" s="14"/>
       <x:c r="M55" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N55" s="14" t="str">
-        <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha. Redraw later as production portraits.</x:v>
+        <x:v>Development reference only; not loaded by the application.</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="34" customHeight="1">
@@ -3193,7 +3188,7 @@
       </x:c>
       <x:c r="L56" s="14"/>
       <x:c r="M56" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N56" s="14" t="str">
         <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha.</x:v>
@@ -3235,7 +3230,7 @@
       </x:c>
       <x:c r="L57" s="14"/>
       <x:c r="M57" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N57" s="14" t="str">
         <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha.</x:v>
@@ -3277,7 +3272,7 @@
       </x:c>
       <x:c r="L58" s="14"/>
       <x:c r="M58" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N58" s="14" t="str">
         <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha.</x:v>
@@ -3319,7 +3314,7 @@
       </x:c>
       <x:c r="L59" s="14"/>
       <x:c r="M59" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N59" s="14" t="str">
         <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha.</x:v>
@@ -3361,7 +3356,7 @@
       </x:c>
       <x:c r="L60" s="14"/>
       <x:c r="M60" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N60" s="14" t="str">
         <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha.</x:v>
@@ -3403,7 +3398,7 @@
       </x:c>
       <x:c r="L61" s="14"/>
       <x:c r="M61" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N61" s="14" t="str">
         <x:v>She/her. Dual-enrollment high school student with a giant iced coffee and matcha.</x:v>
@@ -3411,170 +3406,380 @@
     </x:row>
     <x:row r="62" ht="34" customHeight="1">
       <x:c r="A62" s="14" t="str">
-        <x:v>Optional / future</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="B62" s="14" t="str">
-        <x:v>Branding</x:v>
+        <x:v>Background</x:v>
       </x:c>
       <x:c r="C62" s="14" t="str">
-        <x:v>promptcraft-logo.png</x:v>
+        <x:v>s1-science-wing.jpg</x:v>
       </x:c>
       <x:c r="D62" s="14" t="str">
-        <x:v>assets/images/branding/</x:v>
+        <x:v>assets/images/backgrounds/gfc/</x:v>
       </x:c>
       <x:c r="E62" s="14" t="str">
-        <x:v>assets/images/branding/promptcraft-logo.png</x:v>
+        <x:v>assets/images/backgrounds/gfc/s1-science-wing.jpg</x:v>
       </x:c>
       <x:c r="F62" s="14" t="str">
-        <x:v>Menu, splash, and documentation</x:v>
+        <x:v>S1: Engagement VN/workstation</x:v>
       </x:c>
       <x:c r="G62" s="14" t="str">
-        <x:v>Logo or portrait</x:v>
+        <x:v>GFC campus background</x:v>
       </x:c>
       <x:c r="H62" s="14" t="str">
-        <x:v>PromptCraft logo or wordmark.</x:v>
+        <x:v>Great Falls College Science Wing environment used by S1.</x:v>
       </x:c>
       <x:c r="I62" s="14" t="str">
-        <x:v>Transparent PNG or SVG where appropriate</x:v>
+        <x:v>Landscape JPG, high-resolution</x:v>
       </x:c>
       <x:c r="J62" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K62" s="14" t="str">
-        <x:v>Low</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="L62" s="14"/>
       <x:c r="M62" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N62" s="14" t="str">
-        <x:v>Folder is a planned path and may be created when the asset is approved.</x:v>
+        <x:v>Current V429 scenario background registry.</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="34" customHeight="1">
       <x:c r="A63" s="14" t="str">
-        <x:v>Optional / future</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="B63" s="14" t="str">
-        <x:v>Branding</x:v>
+        <x:v>Background</x:v>
       </x:c>
       <x:c r="C63" s="14" t="str">
-        <x:v>shanel-headshot.png</x:v>
+        <x:v>s2-study-lounge.jpg</x:v>
       </x:c>
       <x:c r="D63" s="14" t="str">
-        <x:v>assets/images/branding/</x:v>
+        <x:v>assets/images/backgrounds/gfc/</x:v>
       </x:c>
       <x:c r="E63" s="14" t="str">
-        <x:v>assets/images/branding/shanel-headshot.png</x:v>
+        <x:v>assets/images/backgrounds/gfc/s2-study-lounge.jpg</x:v>
       </x:c>
       <x:c r="F63" s="14" t="str">
-        <x:v>About PromptCraft panel</x:v>
+        <x:v>S2: Metacognition VN/workstation</x:v>
       </x:c>
       <x:c r="G63" s="14" t="str">
-        <x:v>Logo or portrait</x:v>
+        <x:v>GFC campus background</x:v>
       </x:c>
       <x:c r="H63" s="14" t="str">
-        <x:v>Optional professional headshot.</x:v>
+        <x:v>Great Falls College Study Lounge environment used by S2.</x:v>
       </x:c>
       <x:c r="I63" s="14" t="str">
-        <x:v>Transparent PNG or SVG where appropriate</x:v>
+        <x:v>Landscape JPG, high-resolution</x:v>
       </x:c>
       <x:c r="J63" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K63" s="14" t="str">
-        <x:v>Low</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="L63" s="14"/>
       <x:c r="M63" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N63" s="14" t="str">
-        <x:v>Folder is a planned path and may be created when the asset is approved.</x:v>
+        <x:v>Current V429 scenario background registry.</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="34" customHeight="1">
       <x:c r="A64" s="14" t="str">
-        <x:v>Optional / future</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="B64" s="14" t="str">
-        <x:v>Institutional</x:v>
+        <x:v>UI / Babbage</x:v>
       </x:c>
       <x:c r="C64" s="14" t="str">
-        <x:v>gfcmsu-wordmark.png</x:v>
+        <x:v>babbage-mark.svg</x:v>
       </x:c>
       <x:c r="D64" s="14" t="str">
-        <x:v>assets/images/institutional/</x:v>
+        <x:v>assets/images/ui/</x:v>
       </x:c>
       <x:c r="E64" s="14" t="str">
-        <x:v>assets/images/institutional/gfcmsu-wordmark.png</x:v>
+        <x:v>assets/images/ui/babbage-mark.svg</x:v>
       </x:c>
       <x:c r="F64" s="14" t="str">
-        <x:v>Institutional context panel</x:v>
+        <x:v>PromptCraft brand menus and Babbage identity</x:v>
       </x:c>
       <x:c r="G64" s="14" t="str">
-        <x:v>Logo or portrait</x:v>
+        <x:v>SVG mark</x:v>
       </x:c>
       <x:c r="H64" s="14" t="str">
-        <x:v>Optional Great Falls College MSU wordmark.</x:v>
+        <x:v>Compact Babbage portrait/mark used in PromptCraft branding and interface chrome.</x:v>
       </x:c>
       <x:c r="I64" s="14" t="str">
-        <x:v>Transparent PNG or SVG where appropriate</x:v>
+        <x:v>SVG, transparent</x:v>
       </x:c>
       <x:c r="J64" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K64" s="14" t="str">
-        <x:v>Low</x:v>
+        <x:v>High</x:v>
       </x:c>
       <x:c r="L64" s="14"/>
       <x:c r="M64" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N64" s="14" t="str">
-        <x:v>Folder is a planned path and may be created when the asset is approved.</x:v>
+        <x:v>Current V429 runtime image; asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="34" customHeight="1">
       <x:c r="A65" s="14" t="str">
-        <x:v>Optional / future</x:v>
+        <x:v>Required</x:v>
       </x:c>
       <x:c r="B65" s="14" t="str">
-        <x:v>Institutional</x:v>
+        <x:v>UI / Babbage</x:v>
       </x:c>
       <x:c r="C65" s="14" t="str">
-        <x:v>msu-eds-wordmark.png</x:v>
+        <x:v>charles-babbage.png</x:v>
       </x:c>
       <x:c r="D65" s="14" t="str">
-        <x:v>assets/images/institutional/</x:v>
+        <x:v>assets/images/ui/</x:v>
       </x:c>
       <x:c r="E65" s="14" t="str">
-        <x:v>assets/images/institutional/msu-eds-wordmark.png</x:v>
+        <x:v>assets/images/ui/charles-babbage.png</x:v>
       </x:c>
       <x:c r="F65" s="14" t="str">
-        <x:v>Academic context panel</x:v>
+        <x:v>Meet Babbage page</x:v>
       </x:c>
       <x:c r="G65" s="14" t="str">
-        <x:v>Logo or portrait</x:v>
+        <x:v>Portrait image</x:v>
       </x:c>
       <x:c r="H65" s="14" t="str">
-        <x:v>Optional Montana State University Ed.S. mark.</x:v>
+        <x:v>Charles Babbage portrait used on the Meet Babbage information page.</x:v>
       </x:c>
       <x:c r="I65" s="14" t="str">
-        <x:v>Transparent PNG or SVG where appropriate</x:v>
+        <x:v>PNG</x:v>
       </x:c>
       <x:c r="J65" s="14" t="str">
-        <x:v>Not Started</x:v>
+        <x:v>In Use</x:v>
       </x:c>
       <x:c r="K65" s="14" t="str">
-        <x:v>Low</x:v>
+        <x:v>Medium</x:v>
       </x:c>
       <x:c r="L65" s="14"/>
       <x:c r="M65" s="18" t="n">
-        <x:v>46226</x:v>
+        <x:v>46253</x:v>
       </x:c>
       <x:c r="N65" s="14" t="str">
-        <x:v>Folder is a planned path and may be created when the asset is approved.</x:v>
+        <x:v>Current V429 runtime image; asset-manifest v144.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>Required</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>Background</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>desk-extension.png</x:v>
+      </x:c>
+      <x:c r="D66" t="str">
+        <x:v>assets/images/backgrounds/</x:v>
+      </x:c>
+      <x:c r="E66" t="str">
+        <x:v>assets/images/backgrounds/desk-extension.png</x:v>
+      </x:c>
+      <x:c r="F66" t="str">
+        <x:v>Shared workstation composition</x:v>
+      </x:c>
+      <x:c r="G66" t="str">
+        <x:v>Background extension</x:v>
+      </x:c>
+      <x:c r="H66" t="str">
+        <x:v>Desk/workstation extension used by shared Babbage layouts.</x:v>
+      </x:c>
+      <x:c r="I66" t="str">
+        <x:v>PNG</x:v>
+      </x:c>
+      <x:c r="J66" t="str">
+        <x:v>In Use</x:v>
+      </x:c>
+      <x:c r="K66" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="L66"/>
+      <x:c r="M66" s="77" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="N66" t="str">
+        <x:v>Current V429 runtime image; asset-manifest v144.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>Required</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>Brand / Print</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>great-falls-college-logo.jpg</x:v>
+      </x:c>
+      <x:c r="D67" t="str">
+        <x:v>assets/images/brand/</x:v>
+      </x:c>
+      <x:c r="E67" t="str">
+        <x:v>assets/images/brand/great-falls-college-logo.jpg</x:v>
+      </x:c>
+      <x:c r="F67" t="str">
+        <x:v>Printable Babbage report</x:v>
+      </x:c>
+      <x:c r="G67" t="str">
+        <x:v>Institutional logo</x:v>
+      </x:c>
+      <x:c r="H67" t="str">
+        <x:v>Great Falls College logo used in the document-first printable diagnosis report.</x:v>
+      </x:c>
+      <x:c r="I67" t="str">
+        <x:v>JPG</x:v>
+      </x:c>
+      <x:c r="J67" t="str">
+        <x:v>In Use</x:v>
+      </x:c>
+      <x:c r="K67" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="L67"/>
+      <x:c r="M67" s="77" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="N67" t="str">
+        <x:v>Current V429 runtime image; print/report use.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>Required</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>UI / Babbage</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>babbage-engine.webp</x:v>
+      </x:c>
+      <x:c r="D68" t="str">
+        <x:v>assets/images/ui/</x:v>
+      </x:c>
+      <x:c r="E68" t="str">
+        <x:v>assets/images/ui/babbage-engine.webp</x:v>
+      </x:c>
+      <x:c r="F68" t="str">
+        <x:v>Teaching Progress panel</x:v>
+      </x:c>
+      <x:c r="G68" t="str">
+        <x:v>Historical machine image</x:v>
+      </x:c>
+      <x:c r="H68" t="str">
+        <x:v>Historic Babbage engine image used in the expanded teaching-progression panel.</x:v>
+      </x:c>
+      <x:c r="I68" t="str">
+        <x:v>WEBP</x:v>
+      </x:c>
+      <x:c r="J68" t="str">
+        <x:v>In Use</x:v>
+      </x:c>
+      <x:c r="K68" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="L68"/>
+      <x:c r="M68" s="77" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="N68" t="str">
+        <x:v>Current V429 runtime image; Teaching Progress.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str">
+        <x:v>Reference</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>UI / Babbage</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>babbage-engine-plate.svg</x:v>
+      </x:c>
+      <x:c r="D69" t="str">
+        <x:v>assets/images/ui/</x:v>
+      </x:c>
+      <x:c r="E69" t="str">
+        <x:v>assets/images/ui/babbage-engine-plate.svg</x:v>
+      </x:c>
+      <x:c r="F69" t="str">
+        <x:v>Development reference</x:v>
+      </x:c>
+      <x:c r="G69" t="str">
+        <x:v>Legacy/reference plate</x:v>
+      </x:c>
+      <x:c r="H69" t="str">
+        <x:v>Earlier Babbage engine plate retained only as a development reference.</x:v>
+      </x:c>
+      <x:c r="I69" t="str">
+        <x:v>SVG</x:v>
+      </x:c>
+      <x:c r="J69" t="str">
+        <x:v>Reference Only</x:v>
+      </x:c>
+      <x:c r="K69" t="str">
+        <x:v>Low</x:v>
+      </x:c>
+      <x:c r="L69"/>
+      <x:c r="M69" s="77" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="N69" t="str">
+        <x:v>Not loaded by the current application.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>Required</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>UI / Utility</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>promptcraft-qr.png</x:v>
+      </x:c>
+      <x:c r="D70" t="str">
+        <x:v>assets/ui/</x:v>
+      </x:c>
+      <x:c r="E70" t="str">
+        <x:v>assets/ui/promptcraft-qr.png</x:v>
+      </x:c>
+      <x:c r="F70" t="str">
+        <x:v>Main menu / Prompt Lab launch</x:v>
+      </x:c>
+      <x:c r="G70" t="str">
+        <x:v>QR code</x:v>
+      </x:c>
+      <x:c r="H70" t="str">
+        <x:v>PromptCraft QR code shown in the Prompt Lab landing experience.</x:v>
+      </x:c>
+      <x:c r="I70" t="str">
+        <x:v>PNG</x:v>
+      </x:c>
+      <x:c r="J70" t="str">
+        <x:v>In Use</x:v>
+      </x:c>
+      <x:c r="K70" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="L70"/>
+      <x:c r="M70" s="77" t="n">
+        <x:v>46253</x:v>
+      </x:c>
+      <x:c r="N70" t="str">
+        <x:v>Current V429 runtime image; asset-manifest v144.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3706,7 +3911,7 @@
         <x:v>audio/background.mp3</x:v>
       </x:c>
       <x:c r="L2" s="14" t="str">
-        <x:v>Path verified in the v137 project.</x:v>
+        <x:v>Current V429 runtime audio; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
@@ -3744,7 +3949,7 @@
         <x:v>audio/welcome.mp3</x:v>
       </x:c>
       <x:c r="L3" s="14" t="str">
-        <x:v>Path verified in the v137 project.</x:v>
+        <x:v>Current V429 runtime audio; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
@@ -3782,7 +3987,7 @@
         <x:v>audio/vague.mp3</x:v>
       </x:c>
       <x:c r="L4" s="14" t="str">
-        <x:v>Path verified in the v137 project.</x:v>
+        <x:v>Current V429 runtime audio; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -3820,7 +4025,7 @@
         <x:v>audio/decent.mp3</x:v>
       </x:c>
       <x:c r="L5" s="14" t="str">
-        <x:v>Path verified in the v137 project.</x:v>
+        <x:v>Current V429 runtime audio; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -3858,7 +4063,7 @@
         <x:v>audio/strong.mp3</x:v>
       </x:c>
       <x:c r="L6" s="14" t="str">
-        <x:v>Path verified in the v137 project.</x:v>
+        <x:v>Current V429 runtime audio; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -3896,7 +4101,7 @@
         <x:v>audio/scenario-1-intro.mp3</x:v>
       </x:c>
       <x:c r="L7" s="14" t="str">
-        <x:v>Path verified in the v137 project.</x:v>
+        <x:v>Current V429 runtime audio; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
@@ -3934,7 +4139,7 @@
         <x:v>audio/scenario-complete.mp3</x:v>
       </x:c>
       <x:c r="L8" s="14" t="str">
-        <x:v>Path verified in the v137 project.</x:v>
+        <x:v>Current V429 runtime audio; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
@@ -3972,7 +4177,7 @@
         <x:v>audio/all-complete.mp3</x:v>
       </x:c>
       <x:c r="L9" s="14" t="str">
-        <x:v>Path verified in the v137 project.</x:v>
+        <x:v>Current V429 runtime audio; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
@@ -4010,7 +4215,7 @@
         <x:v>audio/reflection-open.mp3</x:v>
       </x:c>
       <x:c r="L10" s="14" t="str">
-        <x:v>Path verified in the v137 project.</x:v>
+        <x:v>Current V429 runtime audio; classified in asset-manifest v144.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="34" customHeight="1">
@@ -10107,16 +10312,20 @@
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
       <x:c r="A1" s="65" t="str">
-        <x:v>PromptCraft Master Asset Tracker — v137</x:v>
+        <x:v>PromptCraft Master Asset Tracker — V429 / asset manifest v144</x:v>
       </x:c>
       <x:c r="B1" s="65"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2"/>
+      <x:c r="B2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="69" t="str">
         <x:v>Workbook purpose</x:v>
       </x:c>
       <x:c r="B3" s="73" t="str">
-        <x:v>Living production tracker for PromptCraft visual assets, current runtime audio, and planned line-by-line voice recordings.</x:v>
+        <x:v>High-level production inventory for PromptCraft visual assets, current runtime audio, planned audio, and supporting production status.</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -10124,7 +10333,7 @@
         <x:v>Code baseline</x:v>
       </x:c>
       <x:c r="B4" s="73" t="str">
-        <x:v>PromptCraft v137 organized asset structure.</x:v>
+        <x:v>PROMPTCRAFT_V429; current documentation/cache revision 446.</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -10132,7 +10341,7 @@
         <x:v>Visual source of truth</x:v>
       </x:c>
       <x:c r="B5" s="73" t="str">
-        <x:v>index.html, style.css, functions/app.js, and assets/asset-manifest.json.</x:v>
+        <x:v>assets/asset-manifest.json (v144), src/js/app/config-and-assets.js, and current asset files under assets/.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -10140,7 +10349,7 @@
         <x:v>Runtime audio source of truth</x:v>
       </x:c>
       <x:c r="B6" s="73" t="str">
-        <x:v>The ASSETS.audio object and Howler setup in functions/app.js. Runtime Audio lists the files currently connected to the app.</x:v>
+        <x:v>ASSETS.audio in src/js/app/config-and-assets.js plus assets/asset-manifest.json. Runtime Audio lists connected audio and preserved historical references.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -10148,7 +10357,7 @@
         <x:v>Dialogue source of truth</x:v>
       </x:c>
       <x:c r="B7" s="73" t="str">
-        <x:v>functions/dialogue.js for active S1/shared lines. Old S2–S8 lines remain in the tracker as Archived design history.</x:v>
+        <x:v>src/js/content/dialogue-data.js plus scenario-owned dynamic dialogue such as Jordan's S2 intervention responses.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -10156,7 +10365,7 @@
         <x:v>Audio folder convention</x:v>
       </x:c>
       <x:c r="B8" s="73" t="str">
-        <x:v>Music belongs in assets/audio/music/. Voice files are separated by speaker, then by scenario or function.</x:v>
+        <x:v>Music belongs in assets/audio/music/. Voice is separated by speaker, then by scenario or function.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -10164,7 +10373,7 @@
         <x:v>Professor Pixel convention</x:v>
       </x:c>
       <x:c r="B9" s="73" t="str">
-        <x:v>Line-by-line recordings keep p#.mp3 filenames inside the appropriate professor-pixel folder.</x:v>
+        <x:v>Line-by-line recordings use stable IDs/filenames inside the appropriate professor-pixel folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -10172,23 +10381,23 @@
         <x:v>Student convention</x:v>
       </x:c>
       <x:c r="B10" s="73" t="str">
-        <x:v>Student recordings use descriptive IDs such as jordan-s2-01.mp3 inside that student's scenario folder.</x:v>
+        <x:v>Student recordings use stable descriptive IDs such as jordan-s2-intervention-evidence.mp3 inside the student's scenario folder.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="69" t="str">
-        <x:v>S2 draft audio</x:v>
+        <x:v>S2 audio</x:v>
       </x:c>
       <x:c r="B11" s="73" t="str">
-        <x:v>p86–p94 and jordan-s2-01–03 are planned paths only. Their dialogue is still marked Draft / rewrite before recording.</x:v>
+        <x:v>Current S2 dialogue is active as text; listed line recordings are planned until the corresponding audio files are produced.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="69" t="str">
-        <x:v>Legacy audio</x:v>
+        <x:v>Historical audio</x:v>
       </x:c>
       <x:c r="B12" s="73" t="str">
-        <x:v>Old S2–S8 combined recordings are stored under archive/legacy-assets/audio/ and are not loaded by the application.</x:v>
+        <x:v>Archived/legacy rows are reference material only and must not be reconnected without reviewing the redesigned scenario.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -10196,7 +10405,7 @@
         <x:v>Recommended workflow</x:v>
       </x:c>
       <x:c r="B13" s="73" t="str">
-        <x:v>Use Runtime Audio for what the current app loads. Use Audio Assets for recording production and dialogue review.</x:v>
+        <x:v>Use Dashboard for project status, Visual Assets for the consolidated visual inventory, Runtime Audio for connected audio, and dialogue-voiceover-tracker.xlsx for line-by-line recording work.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
